--- a/cards.xlsx
+++ b/cards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\witcher-3-gwent-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1048755-643D-444F-9591-0A767F2E1CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC0271F-60E9-4D44-9040-B93921B4686F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{C7211A38-802B-4C9D-8105-50DCB0156070}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" activeTab="1" xr2:uid="{C7211A38-802B-4C9D-8105-50DCB0156070}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="456">
   <si>
     <t>Name</t>
   </si>
@@ -1402,6 +1402,12 @@
   </si>
   <si>
     <t>"Pillars of flame turn the mightiest to ash. All others tremble in shock and awe."</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>Boolean</t>
   </si>
 </sst>
 </file>
@@ -1684,12 +1690,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0B24B11B-25C1-4271-8792-F4C5E568A516}" name="Table5" displayName="Table5" ref="A1:E23" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
-  <autoFilter ref="A1:E23" xr:uid="{0B24B11B-25C1-4271-8792-F4C5E568A516}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0B24B11B-25C1-4271-8792-F4C5E568A516}" name="Table5" displayName="Table5" ref="A1:F23" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
+  <autoFilter ref="A1:F23" xr:uid="{0B24B11B-25C1-4271-8792-F4C5E568A516}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7DD889D8-99BA-4372-8BB6-C913758431CD}" name="Name" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{3E6296FE-A3CF-42D6-908B-377E4A25A153}" name="Faction" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{B99928AF-BA64-4D68-A4ED-505719138EAE}" name="DLC" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{C31574EC-4D78-454A-B164-8F7A6DACA165}" name="Passive"/>
     <tableColumn id="5" xr3:uid="{BA43C6E1-AECC-4F3B-9416-61AF1194CEDE}" name="Ability" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{6FFD4C43-EEA5-4CC4-9FE7-4192D61F1E83}" name="Quote" dataDxfId="0"/>
   </tableColumns>
@@ -7314,17 +7321,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1260A867-074C-49A3-ACE9-5EA609B6D64C}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="37.53515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.23046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="110.07421875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.07421875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="110.07421875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="77.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7335,13 +7343,16 @@
         <v>148</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -7352,13 +7363,16 @@
         <v>184</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>231</v>
       </c>
@@ -7366,13 +7380,16 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" t="s">
         <v>215</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>56</v>
       </c>
@@ -7381,13 +7398,16 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>156</v>
       </c>
@@ -7398,13 +7418,16 @@
         <v>183</v>
       </c>
       <c r="D5" t="s">
+        <v>448</v>
+      </c>
+      <c r="E5" t="s">
         <v>213</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>57</v>
       </c>
@@ -7413,13 +7436,16 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -7427,13 +7453,16 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E7" t="s">
         <v>217</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>149</v>
       </c>
@@ -7444,13 +7473,16 @@
         <v>183</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -7458,13 +7490,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" t="s">
         <v>209</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>115</v>
       </c>
@@ -7473,13 +7508,16 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>116</v>
       </c>
@@ -7487,13 +7525,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E11" t="s">
         <v>211</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>117</v>
       </c>
@@ -7502,13 +7543,16 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -7516,13 +7560,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
+        <v>238</v>
+      </c>
+      <c r="E13" t="s">
         <v>202</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>35</v>
       </c>
@@ -7531,13 +7578,16 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>204</v>
       </c>
@@ -7548,13 +7598,16 @@
         <v>183</v>
       </c>
       <c r="D15" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" t="s">
         <v>205</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
@@ -7563,13 +7616,16 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -7577,13 +7633,16 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" t="s">
         <v>207</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>88</v>
       </c>
@@ -7592,13 +7651,16 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>157</v>
       </c>
@@ -7609,13 +7671,16 @@
         <v>183</v>
       </c>
       <c r="D19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" t="s">
         <v>219</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>89</v>
       </c>
@@ -7624,13 +7689,16 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -7638,13 +7706,16 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" t="s">
         <v>221</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
         <v>91</v>
       </c>
@@ -7653,13 +7724,16 @@
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>175</v>
       </c>
@@ -7670,9 +7744,12 @@
         <v>184</v>
       </c>
       <c r="D23" t="s">
+        <v>448</v>
+      </c>
+      <c r="E23" t="s">
         <v>224</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>385</v>
       </c>
     </row>
@@ -7683,7 +7760,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E48CDE98-4B24-44EF-9918-91D94D059C11}">
           <x14:formula1>
             <xm:f>Types!$C$2:$C$4</xm:f>
@@ -7695,6 +7772,12 @@
             <xm:f>Factions!$A$2:$A$7</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8364381C-1143-4839-A0FE-9EEB9E6A0735}">
+          <x14:formula1>
+            <xm:f>Types!$D$2:$D$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7922,14 +8005,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E03B57-3BD9-4B95-9BE1-E0740EDA349D}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.23046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>201</v>
       </c>
@@ -7939,8 +8022,11 @@
       <c r="C1" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D1" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -7950,8 +8036,11 @@
       <c r="C2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7961,8 +8050,11 @@
       <c r="C3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -7973,17 +8065,17 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>6</v>
       </c>
